--- a/stick-world/config/excel/单位数据.xlsx
+++ b/stick-world/config/excel/单位数据.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="stickmen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="weapons" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="armors" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="火柴人" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="武器" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="盔甲" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,16 @@
       <name val="Microsoft YaHei"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -79,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,6 +102,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -537,74 +551,70 @@
           <t>description</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>race: plain/volcano/source/desert/ocean/forest/ice</t>
-        </is>
-      </c>
+      <c r="N1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>唯一ID</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>中文名称</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>种族</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>变体</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>基础生命值</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>基础攻击力</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>基础防御力</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>基础速度</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>基础耐力</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>沥青消耗</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>图标路径</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>variant: normal/giant/long_arm/centaur/winged/multi_head</t>
         </is>
@@ -837,59 +847,59 @@
           <t>icon_path</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>type: sword/spear/bow/crossbow/staff/bare_hand</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>唯一ID</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>中文名称</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>武器类型</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>攻击倍率</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>速度倍率</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>射程加成</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>穿甲值</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>沥青消耗</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>图标路径</t>
         </is>
@@ -1116,49 +1126,49 @@
           <t>icon_path</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>type: cloth/leather/chain/plate/magic_shield</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>唯一ID</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>中文名称</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>盔甲类型</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>伤害减免</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>速度惩罚</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>沥青消耗</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>图标路径</t>
         </is>

--- a/stick-world/config/excel/单位数据.xlsx
+++ b/stick-world/config/excel/单位数据.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="火柴人" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,14 +11,14 @@
     <sheet name="盔甲" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,20 +33,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00666666"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00999999"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
@@ -56,8 +41,12 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +58,9 @@
         <fgColor rgb="00D9D9D9"/>
         <bgColor rgb="00D9D9D9"/>
       </patternFill>
+    </fill>
+    <fill>
+      <patternFill/>
     </fill>
   </fills>
   <borders count="2">
@@ -84,35 +76,32 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -473,300 +462,833 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="5" max="10"/>
     <col width="42" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name_zh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>race</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>variant</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>base_template</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>base_hp</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>base_attack</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>base_defense</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>base_speed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>base_stamina</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>asphalt_cost</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>icon_path</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="N1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>唯一ID</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>中文名称</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>种族</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>变体</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>原生模板(变种时填写)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>基础生命值</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>基础攻击力</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>基础防御力</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>基础速度</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>基础耐力</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>沥青消耗</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>图标路径</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
-        <is>
-          <t>variant: normal/giant/long_arm/centaur/winged/multi_head</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>stm_plain_001</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>平原步兵</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>火柴人</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>plain</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>res://assets/icons/stickmen/plain_normal.png</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>基础平原火柴人，均衡型</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stickmen/plain.png</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>标准体型，均衡型农耕种族</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>stm_volcano_giant_001</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>火山巨人</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>stm_volcano_001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>火山火柴人</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>volcano</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stickmen/volcano.png</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>带岩浆纹，粗壮，冶炼锻造专精</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>stm_snow_001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>雪地火柴人</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>snow</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stickmen/snow.png</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>霜白纹理，耐寒，冰系法术倾向</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>stm_giant_001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>巨人</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>giant</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>res://assets/icons/stickmen/volcano_giant.png</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>火山巨人，高生命高攻击，速度慢</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>stm_ocean_winged_001</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>海洋翼人</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>ocean</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stickmen/giant.png</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4人高，生活在高山地区，可被奴役运输</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>stm_mage_001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>术士</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mage</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stickmen/mage.png</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>法系种族，体质较弱但法术攻击高</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>stm_dwarf_001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>矮人</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>dwarf</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stickmen/dwarf.png</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>矮小健壮，耐力好，适合采矿建造</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>stm_centaur_001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>半人马</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>centaur</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stickmen/centaur.png</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>四足下身，速度极快，骑乘/侦察</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>stm_winged_001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>羽翼火柴人</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>winged</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>res://assets/icons/stickmen/ocean_winged.png</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>海洋翼人，高速度高耐力，可飞行</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stickmen/winged.png</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>背部翼膜可滑翔，侦察传信</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>stm_long_arm_001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>长臂人</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>long_arm</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>plain</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>平原火柴人变种，双臂超长，投石/采集专精</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>stm_giant_enslaved</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>被奴役巨人</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>被铁链和军事人员押送的巨人，用于重物运输</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>stm_zombie_001</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>僵尸</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>zombie</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>plain</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stickmen/zombie.png</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>火柴人的僵尸化变种，行动缓慢但耐力极高</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>stm_corrupted_mage_001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>失控术士</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>corrupted_mage</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>mage</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stickmen/corrupted_mage.png</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>术士的失控变种，法术攻击极高但脆弱不堪</t>
         </is>
       </c>
     </row>
@@ -782,14 +1304,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -847,59 +1367,59 @@
           <t>icon_path</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>type: sword/spear/bow/crossbow/staff/bare_hand</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>唯一ID</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>中文名称</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>武器类型</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>攻击倍率</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>速度倍率</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>射程加成</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>穿甲值</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>沥青消耗</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>图标路径</t>
         </is>
@@ -1059,7 +1579,7 @@
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1073,11 +1593,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -1126,49 +1645,49 @@
           <t>icon_path</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>type: cloth/leather/chain/plate/magic_shield</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>唯一ID</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>中文名称</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>盔甲类型</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>伤害减免</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>速度惩罚</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>沥青消耗</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>图标路径</t>
         </is>

--- a/stick-world/config/excel/单位数据.xlsx
+++ b/stick-world/config/excel/单位数据.xlsx
@@ -6,9 +6,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="火柴人" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="武器" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="盔甲" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="stickmen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="weapons" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="armors" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -477,612 +477,557 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name_zh</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>base_template</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>base_hp</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>base_attack</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>base_defense</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>base_speed</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>base_stamina</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>asphalt_cost</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>icon_path</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>description</t>
+          <t>#output_dir: units</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>唯一ID</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>中文名称</t>
+          <t>name_zh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>种族</t>
+          <t>race</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>原生模板(变种时填写)</t>
+          <t>base_template</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>基础生命值</t>
+          <t>base_hp</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>基础攻击力</t>
+          <t>base_attack</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>基础防御力</t>
+          <t>base_defense</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>基础速度</t>
+          <t>base_speed</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>基础耐力</t>
+          <t>base_stamina</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>沥青消耗</t>
+          <t>asphalt_cost</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>图标路径</t>
+          <t>icon_path</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>description</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stm_plain_001</t>
+          <t>唯一ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>火柴人</t>
+          <t>中文名称</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>plain</t>
+          <t>种族</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>原生模板(变种时填写)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>基础生命值</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>基础攻击力</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>基础防御力</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>基础速度</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>基础耐力</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>沥青消耗</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>res://assets/icons/stickmen/plain.png</t>
+          <t>图标路径</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>标准体型，均衡型农耕种族</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stm_volcano_001</t>
+          <t>stm_plain_001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>火山火柴人</t>
+          <t>火柴人</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>volcano</t>
+          <t>plain</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>res://assets/icons/stickmen/volcano.png</t>
+          <t>res://assets/icons/stickmen/plain.png</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>带岩浆纹，粗壮，冶炼锻造专精</t>
+          <t>标准体型，均衡型农耕种族</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>stm_snow_001</t>
+          <t>stm_volcano_001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>雪地火柴人</t>
+          <t>火山火柴人</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>volcano</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>res://assets/icons/stickmen/snow.png</t>
+          <t>res://assets/icons/stickmen/volcano.png</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>霜白纹理，耐寒，冰系法术倾向</t>
+          <t>带岩浆纹，粗壮，冶炼锻造专精</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>stm_giant_001</t>
+          <t>stm_snow_001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>巨人</t>
+          <t>雪地火柴人</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>res://assets/icons/stickmen/giant.png</t>
+          <t>res://assets/icons/stickmen/snow.png</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4人高，生活在高山地区，可被奴役运输</t>
+          <t>霜白纹理，耐寒，冰系法术倾向</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>stm_mage_001</t>
+          <t>stm_giant_001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>术士</t>
+          <t>巨人</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mage</t>
+          <t>giant</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>400</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>res://assets/icons/stickmen/mage.png</t>
+          <t>res://assets/icons/stickmen/giant.png</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>法系种族，体质较弱但法术攻击高</t>
+          <t>4人高，生活在高山地区，可被奴役运输</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>stm_dwarf_001</t>
+          <t>stm_mage_001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>矮人</t>
+          <t>术士</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dwarf</t>
+          <t>mage</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>res://assets/icons/stickmen/dwarf.png</t>
+          <t>res://assets/icons/stickmen/mage.png</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>矮小健壮，耐力好，适合采矿建造</t>
+          <t>法系种族，体质较弱但法术攻击高</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>stm_centaur_001</t>
+          <t>stm_dwarf_001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>半人马</t>
+          <t>矮人</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>centaur</t>
+          <t>dwarf</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>res://assets/icons/stickmen/centaur.png</t>
+          <t>res://assets/icons/stickmen/dwarf.png</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>四足下身，速度极快，骑乘/侦察</t>
+          <t>矮小健壮，耐力好，适合采矿建造</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stm_winged_001</t>
+          <t>stm_centaur_001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>羽翼火柴人</t>
+          <t>半人马</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>winged</t>
+          <t>centaur</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>res://assets/icons/stickmen/winged.png</t>
+          <t>res://assets/icons/stickmen/centaur.png</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>背部翼膜可滑翔，侦察传信</t>
+          <t>四足下身，速度极快，骑乘/侦察</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stm_long_arm_001</t>
+          <t>stm_winged_001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>长臂人</t>
+          <t>羽翼火柴人</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>long_arm</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>plain</t>
+          <t>winged</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1092,201 +1037,263 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stickmen/winged.png</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>平原火柴人变种，双臂超长，投石/采集专精</t>
+          <t>背部翼膜可滑翔，侦察传信</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>stm_giant_enslaved</t>
+          <t>stm_long_arm_001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>被奴役巨人</t>
+          <t>长臂人</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>long_arm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>plain</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>被铁链和军事人员押送的巨人，用于重物运输</t>
+          <t>平原火柴人变种，双臂超长，投石/采集专精</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stm_zombie_001</t>
+          <t>stm_giant_enslaved</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>僵尸</t>
+          <t>被奴役巨人</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>zombie</t>
+          <t>giant</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>plain</t>
+          <t>giant</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>400</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>res://assets/icons/stickmen/zombie.png</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>火柴人的僵尸化变种，行动缓慢但耐力极高</t>
+          <t>被铁链和军事人员押送的巨人，用于重物运输</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>stm_zombie_001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>僵尸</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>zombie</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>plain</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>res://assets/icons/stickmen/zombie.png</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>火柴人的僵尸化变种，行动缓慢但耐力极高</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>stm_corrupted_mage_001</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>失控术士</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>corrupted_mage</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>mage</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>res://assets/icons/stickmen/corrupted_mage.png</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>术士的失控变种，法术攻击极高但脆弱不堪</t>
         </is>
@@ -1303,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1317,269 +1324,277 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#output_dir: units</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>name_zh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>attack_mult</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>speed_mult</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>range_bonus</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>armor_penetration</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>asphalt_cost</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>icon_path</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>唯一ID</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>中文名称</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>武器类型</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>攻击倍率</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>速度倍率</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>射程加成</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>穿甲值</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>沥青消耗</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>图标路径</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>type: sword/spear/bow/crossbow/staff/bare_hand</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>唯一ID</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>中文名称</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>武器类型</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>攻击倍率</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>速度倍率</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>射程加成</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>穿甲值</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>沥青消耗</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>图标路径</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>wpn_sword_001</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>铁剑</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>sword</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>res://assets/icons/weapons/sword_iron.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>wpn_bow_001</t>
+          <t>wpn_sword_001</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>短弓</t>
+          <t>铁剑</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>bow</t>
+          <t>sword</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>res://assets/icons/weapons/bow_short.png</t>
+          <t>res://assets/icons/weapons/sword_iron.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>wpn_staff_001</t>
+          <t>wpn_bow_001</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>学徒法杖</t>
+          <t>短弓</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>bow</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="H5" s="5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>res://assets/icons/weapons/staff_apprentice.png</t>
+          <t>res://assets/icons/weapons/bow_short.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>wpn_bare_001</t>
+          <t>wpn_staff_001</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>徒手</t>
+          <t>学徒法杖</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>bare_hand</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>res://assets/icons/weapons/staff_apprentice.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>wpn_bare_001</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>徒手</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>bare_hand</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1592,7 +1607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1605,259 +1620,267 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#output_dir: units</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>name_zh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>damage_reduction</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>speed_penalty</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>asphalt_cost</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>icon_path</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>唯一ID</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>中文名称</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>盔甲类型</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>伤害减免</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>速度惩罚</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>沥青消耗</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>图标路径</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>type: cloth/leather/chain/plate/magic_shield</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>唯一ID</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>中文名称</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>盔甲类型</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>伤害减免</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>速度惩罚</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>沥青消耗</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>图标路径</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>arm_cloth_001</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>布衣</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>cloth</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>res://assets/icons/armors/cloth_robe.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>arm_leather_001</t>
+          <t>arm_cloth_001</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>皮甲</t>
+          <t>布衣</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>cloth</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>res://assets/icons/armors/leather_vest.png</t>
+          <t>res://assets/icons/armors/cloth_robe.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>arm_chain_001</t>
+          <t>arm_leather_001</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>锁子甲</t>
+          <t>皮甲</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>chain</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>res://assets/icons/armors/chain_mail.png</t>
+          <t>res://assets/icons/armors/leather_vest.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>arm_plate_001</t>
+          <t>arm_chain_001</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>板甲</t>
+          <t>锁子甲</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>plate</t>
+          <t>chain</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>80</v>
-      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>res://assets/icons/armors/plate_armor.png</t>
+          <t>res://assets/icons/armors/chain_mail.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>arm_plate_001</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>板甲</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>plate</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>res://assets/icons/armors/plate_armor.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
           <t>arm_magic_001</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>魔法护盾</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>magic_shield</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G8" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>res://assets/icons/armors/magic_shield.png</t>
         </is>

--- a/stick-world/config/excel/单位数据.xlsx
+++ b/stick-world/config/excel/单位数据.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>base_template</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -540,6 +540,16 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>description</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>attack_cooldown</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>head_shot_bonus_damage</t>
         </is>
       </c>
     </row>
@@ -561,7 +571,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>原生模板(变种时填写)</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -602,6 +612,16 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>描述</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>attack_cooldown</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>head_shot_bonus_damage</t>
         </is>
       </c>
     </row>
@@ -613,7 +633,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>火柴人</t>
+          <t>平原步兵</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -621,56 +641,51 @@
           <t>plain</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="n">
+        <v>50</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>res://assets/icons/stickmen/plain.png</t>
+          <t>res://assets/icons/stickmen/plain_normal.png</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>标准体型，均衡型农耕种族</t>
+          <t>基础平原火柴人，均衡型</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>stm_volcano_001</t>
+          <t>stm_volcano_giant_001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>火山火柴人</t>
+          <t>火山巨人</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -678,624 +693,411 @@
           <t>volcano</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>250</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>80</v>
+      </c>
+      <c r="J5" t="n">
+        <v>120</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>res://assets/icons/stickmen/volcano.png</t>
+          <t>res://assets/icons/stickmen/volcano_giant.png</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>带岩浆纹，粗壮，冶炼锻造专精</t>
+          <t>火山巨人，高生命高攻击，速度慢</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>stm_snow_001</t>
+          <t>stm_ocean_winged_001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>雪地火柴人</t>
+          <t>海洋翼人</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>snow</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+          <t>ocean</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>winged</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>80</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="I6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J6" t="n">
+        <v>80</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>res://assets/icons/stickmen/snow.png</t>
+          <t>res://assets/icons/stickmen/ocean_winged.png</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>霜白纹理，耐寒，冰系法术倾向</t>
+          <t>海洋翼人，高速度高耐力，可飞行</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>stm_giant_001</t>
+          <t>stm_sword_001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>巨人</t>
+          <t>剑士</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>giant</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sword</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>80</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>res://assets/icons/stickmen/giant.png</t>
-        </is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>125</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4人高，生活在高山地区，可被奴役运输</t>
+          <t>SWL Swordwrath 校准（P5 数值批次：namu wiki Normal 模式面板值，HP80/伤12/攻速1.0/s/价125金）</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>stm_mage_001</t>
+          <t>stm_spear_001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>术士</t>
+          <t>矛士</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mage</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>spear</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>440</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>res://assets/icons/stickmen/mage.png</t>
-        </is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>500</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>法系种族，体质较弱但法术攻击高</t>
+          <t>SWL Spearton 校准（HP440/伤15/攻速2s/价500金）</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>stm_dwarf_001</t>
+          <t>stm_bow_001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>矮人</t>
+          <t>弓手</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dwarf</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>bow</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>res://assets/icons/stickmen/dwarf.png</t>
-        </is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>300</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>矮小健壮，耐力好，适合采矿建造</t>
-        </is>
+          <t>SWL Archidon 校准（HP70/身伤10+爆头加值22=32/攻速2s/价300金）</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stm_centaur_001</t>
+          <t>stm_miner_001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>半人马</t>
+          <t>矿工</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>centaur</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>pickaxe</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>res://assets/icons/stickmen/centaur.png</t>
-        </is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>150</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>四足下身，速度极快，骑乘/侦察</t>
+          <t>SWL Miner 校准（HP100/伤10/攻速1.25即0.8s/价150金）</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stm_winged_001</t>
+          <t>stm_staff_001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>羽翼火柴人</t>
+          <t>法师</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>winged</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>150</v>
+      </c>
+      <c r="F11" t="n">
+        <v>50</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>res://assets/icons/stickmen/winged.png</t>
-        </is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1200</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>背部翼膜可滑翔，侦察传信</t>
+          <t>SWL Magikill 校准（HP150/爆炸伤50/施法冷却~7s/召唤冷却~5s/价1200金）</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>7.0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>stm_long_arm_001</t>
+          <t>stm_giant_001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>长臂人</t>
+          <t>巨人</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>long_arm</t>
+          <t>order</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>plain</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>25</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1500</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>平原火柴人变种，双臂超长，投石/采集专精</t>
+          <t>SWL Giant 校准（HP1000/伤25/挥击~2.5s/价1500金；P8 巨人批次消费）</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2.5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stm_giant_enslaved</t>
+          <t>stm_meric_001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>被奴役巨人</t>
+          <t>祭司</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>order</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>giant</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>meric</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>150</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>被铁链和军事人员押送的巨人，用于重物运输</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>stm_zombie_001</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>僵尸</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>zombie</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>plain</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>res://assets/icons/stickmen/zombie.png</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>火柴人的僵尸化变种，行动缓慢但耐力极高</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>stm_corrupted_mage_001</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>失控术士</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>corrupted_mage</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>mage</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>res://assets/icons/stickmen/corrupted_mage.png</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>术士的失控变种，法术攻击极高但脆弱不堪</t>
+          <t>SWL Meric 占位（本地无 wiki 真值，全推断初值待实测校准——决策点 7：HP150/无近战 base_attack=0 不消费/治疗量冷却射程走行为档案 heal_* 字段族；P7 批次 7b 消费）</t>
         </is>
       </c>
     </row>
